--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9E001-D1AE-4E81-9D73-2EE8A3981977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF6E4DF-393E-4D2B-A999-71A9DF6C7F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
   <si>
     <t>päivä</t>
   </si>
@@ -187,6 +187,21 @@
   </si>
   <si>
     <t>PuMa A3</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>27-25,25-23</t>
+  </si>
+  <si>
+    <t>25-12,25-11</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>25-19,25-23</t>
   </si>
 </sst>
 </file>
@@ -693,11 +708,11 @@
       </c>
       <c r="C2" s="10">
         <f>'A 2025-2026'!R2</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="10">
         <f>'A 2025-2026'!O2</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" s="10">
         <f>'A 2025-2026'!P2</f>
@@ -709,7 +724,7 @@
       </c>
       <c r="G2" s="10">
         <f>'A 2025-2026'!O3</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H2" s="10">
         <f>'A 2025-2026'!Q3</f>
@@ -717,11 +732,11 @@
       </c>
       <c r="I2" s="10">
         <f>'A 2025-2026'!O4</f>
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="J2" s="10">
         <f>'A 2025-2026'!Q4</f>
-        <v>580</v>
+        <v>693</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -745,11 +760,11 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="11">
         <f t="shared" si="0"/>
@@ -761,7 +776,7 @@
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
@@ -769,11 +784,11 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" si="0"/>
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>580</v>
+        <v>693</v>
       </c>
       <c r="K4" s="10"/>
     </row>
@@ -877,7 +892,7 @@
       </c>
       <c r="O2" s="10">
         <f>SUM(H2:H25)+SUM(G2:G25)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P2" s="10">
         <f>SUM(I2:I29)</f>
@@ -889,7 +904,7 @@
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -929,7 +944,7 @@
       </c>
       <c r="O3" s="8">
         <f>SUM(H2:H27)*2+SUM(I2:I279)+SUM(G2:G27)*3</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
@@ -938,7 +953,7 @@
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -978,16 +993,16 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K30)</f>
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L30)</f>
-        <v>580</v>
+        <v>693</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>1124</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1307,14 +1322,24 @@
       <c r="D13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="K13" s="8">
+        <v>52</v>
+      </c>
+      <c r="L13" s="8">
+        <v>48</v>
+      </c>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
@@ -1335,14 +1360,24 @@
       <c r="D14" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="G14" s="22"/>
-      <c r="H14" s="10"/>
+      <c r="H14" s="10">
+        <v>1</v>
+      </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="K14" s="10">
+        <v>50</v>
+      </c>
+      <c r="L14" s="10">
+        <v>23</v>
+      </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
@@ -1363,14 +1398,24 @@
       <c r="D15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="16"/>
+      <c r="E15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
+      <c r="K15" s="8">
+        <v>50</v>
+      </c>
+      <c r="L15" s="8">
+        <v>42</v>
+      </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>

--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF6E4DF-393E-4D2B-A999-71A9DF6C7F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB57ACC-38F3-4259-A444-CBAA7F45D23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>päivä</t>
   </si>
@@ -295,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -344,6 +344,18 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,7 +812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="18" width="10.77734375" customWidth="1"/>
@@ -891,15 +903,15 @@
         <v>8</v>
       </c>
       <c r="O2" s="10">
-        <f>SUM(H2:H25)+SUM(G2:G25)</f>
+        <f>SUM(H2:H23)+SUM(G2:G23)</f>
         <v>7</v>
       </c>
       <c r="P2" s="10">
-        <f>SUM(I2:I29)</f>
+        <f>SUM(I2:I27)</f>
         <v>0</v>
       </c>
       <c r="Q2" s="10">
-        <f>SUM(J2:J29)</f>
+        <f>SUM(J2:J27)</f>
         <v>7</v>
       </c>
       <c r="R2" s="10">
@@ -943,12 +955,12 @@
         <v>4</v>
       </c>
       <c r="O3" s="8">
-        <f>SUM(H2:H27)*2+SUM(I2:I279)+SUM(G2:G27)*3</f>
+        <f>SUM(H2:H25)*2+SUM(I2:I277)+SUM(G2:G25)*3</f>
         <v>15</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
-        <f>SUM(J2:J27)*2+SUM(I2:I29)+H9</f>
+        <f>SUM(J2:J25)*2+SUM(I2:I27)+H9</f>
         <v>15</v>
       </c>
       <c r="R3" s="8">
@@ -992,12 +1004,12 @@
         <v>9</v>
       </c>
       <c r="O4" s="10">
-        <f>SUM(K2:K30)</f>
+        <f>SUM(K2:K28)</f>
         <v>696</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
-        <f>SUM(L2:L30)</f>
+        <f>SUM(L2:L28)</f>
         <v>693</v>
       </c>
       <c r="R4" s="10">
@@ -1423,14 +1435,22 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
+    <row r="16" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>46144</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="20"/>
       <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
+      <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
@@ -1443,34 +1463,50 @@
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
+    <row r="17" spans="1:18" s="29" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23">
+        <v>46144</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+    </row>
+    <row r="18" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>46144</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="20"/>
       <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
@@ -1488,7 +1524,7 @@
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1528,7 +1564,7 @@
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="16"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1568,7 +1604,7 @@
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
-      <c r="E23" s="17"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="16"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1584,51 +1620,27 @@
       <c r="R23" s="8"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="5"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -1636,24 +1648,8 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB57ACC-38F3-4259-A444-CBAA7F45D23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C02071-A2CD-46CB-8683-2DD94477746F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1620" yWindow="636" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
   <si>
     <t>päivä</t>
   </si>
@@ -198,10 +198,13 @@
     <t>25-12,25-11</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
     <t>25-19,25-23</t>
+  </si>
+  <si>
+    <t>26-24,25-17,25-17</t>
+  </si>
+  <si>
+    <t>25-16-25-15,25-14</t>
   </si>
 </sst>
 </file>
@@ -295,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -344,7 +347,6 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -720,11 +722,11 @@
       </c>
       <c r="C2" s="10">
         <f>'A 2025-2026'!R2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="10">
         <f>'A 2025-2026'!O2</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="10">
         <f>'A 2025-2026'!P2</f>
@@ -736,7 +738,7 @@
       </c>
       <c r="G2" s="10">
         <f>'A 2025-2026'!O3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H2" s="10">
         <f>'A 2025-2026'!Q3</f>
@@ -744,11 +746,11 @@
       </c>
       <c r="I2" s="10">
         <f>'A 2025-2026'!O4</f>
-        <v>696</v>
+        <v>847</v>
       </c>
       <c r="J2" s="10">
         <f>'A 2025-2026'!Q4</f>
-        <v>693</v>
+        <v>796</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -772,11 +774,11 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="11">
         <f t="shared" si="0"/>
@@ -788,7 +790,7 @@
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
@@ -796,11 +798,11 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" si="0"/>
-        <v>696</v>
+        <v>847</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>693</v>
+        <v>796</v>
       </c>
       <c r="K4" s="10"/>
     </row>
@@ -815,7 +817,9 @@
   <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="10.77734375" customWidth="1"/>
+    <col min="1" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="18" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -904,7 +908,7 @@
       </c>
       <c r="O2" s="10">
         <f>SUM(H2:H23)+SUM(G2:G23)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P2" s="10">
         <f>SUM(I2:I27)</f>
@@ -916,7 +920,7 @@
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -956,7 +960,7 @@
       </c>
       <c r="O3" s="8">
         <f>SUM(H2:H25)*2+SUM(I2:I277)+SUM(G2:G25)*3</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
@@ -965,7 +969,7 @@
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -1005,16 +1009,16 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K28)</f>
-        <v>696</v>
+        <v>847</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L28)</f>
-        <v>693</v>
+        <v>796</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>1389</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1411,10 +1415,10 @@
         <v>49</v>
       </c>
       <c r="E15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>54</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8">
@@ -1435,7 +1439,7 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" spans="1:19" s="24" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>46144</v>
       </c>
@@ -1446,16 +1450,26 @@
         <v>23</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1</v>
+      </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="K16" s="10">
+        <v>76</v>
+      </c>
+      <c r="L16" s="10">
+        <v>58</v>
+      </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
@@ -1463,47 +1477,49 @@
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
     </row>
-    <row r="17" spans="1:18" s="29" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="28" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23">
         <v>46144</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-    </row>
-    <row r="18" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
-        <v>46144</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="20" t="s">
+      <c r="B17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>49</v>
       </c>
+      <c r="E17" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="26">
+        <v>1</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27">
+        <v>75</v>
+      </c>
+      <c r="L17" s="27">
+        <v>45</v>
+      </c>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+    </row>
+    <row r="18" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="22"/>
       <c r="G18" s="10"/>

--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C02071-A2CD-46CB-8683-2DD94477746F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61146E63-CBC4-4B68-A5CB-6679AB5DC36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="636" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
   <si>
     <t>päivä</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>25-16-25-15,25-14</t>
+  </si>
+  <si>
+    <t>Äht U</t>
   </si>
 </sst>
 </file>
@@ -972,7 +975,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>45962</v>
       </c>
@@ -1516,10 +1519,18 @@
       <c r="R17" s="27"/>
     </row>
     <row r="18" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
+      <c r="A18" s="19">
+        <v>46157</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="E18" s="20"/>
       <c r="F18" s="22"/>
       <c r="G18" s="10"/>
@@ -1536,10 +1547,18 @@
       <c r="R18" s="10"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="A19" s="18">
+        <v>46157</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
@@ -1556,10 +1575,18 @@
       <c r="R19" s="8"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="A20" s="19">
+        <v>46157</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="E20" s="21"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>

--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61146E63-CBC4-4B68-A5CB-6679AB5DC36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EF250C-72DF-4155-8A89-2A20F77C3246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1536" yWindow="960" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
     <t>päivä</t>
   </si>
@@ -208,6 +208,15 @@
   </si>
   <si>
     <t>Äht U</t>
+  </si>
+  <si>
+    <t>25-17,18-25,15-5</t>
+  </si>
+  <si>
+    <t>16-25,17-25</t>
+  </si>
+  <si>
+    <t>14-25,21-25</t>
   </si>
 </sst>
 </file>
@@ -725,11 +734,11 @@
       </c>
       <c r="C2" s="10">
         <f>'A 2025-2026'!R2</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="10">
         <f>'A 2025-2026'!O2</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="10">
         <f>'A 2025-2026'!P2</f>
@@ -737,23 +746,23 @@
       </c>
       <c r="F2" s="10">
         <f>'A 2025-2026'!Q2</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" s="10">
         <f>'A 2025-2026'!O3</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" s="10">
         <f>'A 2025-2026'!Q3</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I2" s="10">
         <f>'A 2025-2026'!O4</f>
-        <v>847</v>
+        <v>973</v>
       </c>
       <c r="J2" s="10">
         <f>'A 2025-2026'!Q4</f>
-        <v>796</v>
+        <v>943</v>
       </c>
       <c r="K2" s="10"/>
     </row>
@@ -777,11 +786,11 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="11">
         <f t="shared" si="0"/>
@@ -789,23 +798,23 @@
       </c>
       <c r="F4" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I4" s="12">
         <f t="shared" si="0"/>
-        <v>847</v>
+        <v>973</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="0"/>
-        <v>796</v>
+        <v>943</v>
       </c>
       <c r="K4" s="10"/>
     </row>
@@ -911,7 +920,7 @@
       </c>
       <c r="O2" s="10">
         <f>SUM(H2:H23)+SUM(G2:G23)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P2" s="10">
         <f>SUM(I2:I27)</f>
@@ -919,11 +928,11 @@
       </c>
       <c r="Q2" s="10">
         <f>SUM(J2:J27)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -963,16 +972,16 @@
       </c>
       <c r="O3" s="8">
         <f>SUM(H2:H25)*2+SUM(I2:I277)+SUM(G2:G25)*3</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*2+SUM(I2:I27)+H9</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1012,16 +1021,16 @@
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K28)</f>
-        <v>847</v>
+        <v>973</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L28)</f>
-        <v>796</v>
+        <v>943</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>1643</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1531,14 +1540,24 @@
       <c r="D18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>57</v>
+      </c>
       <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="K18" s="10">
+        <v>58</v>
+      </c>
+      <c r="L18" s="10">
+        <v>47</v>
+      </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
@@ -1559,14 +1578,24 @@
       <c r="D19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="E19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <v>33</v>
+      </c>
+      <c r="L19" s="8">
+        <v>50</v>
+      </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
@@ -1587,14 +1616,24 @@
       <c r="D20" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>59</v>
+      </c>
       <c r="G20" s="22"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="J20" s="10">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10">
+        <v>35</v>
+      </c>
+      <c r="L20" s="10">
+        <v>50</v>
+      </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>

--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EF250C-72DF-4155-8A89-2A20F77C3246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812B7025-59A9-4042-A33D-8747002FC975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="960" windowWidth="20952" windowHeight="12816" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1764" yWindow="732" windowWidth="21276" windowHeight="12948" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
-    <sheet name="A 2025-2026" sheetId="18" r:id="rId2"/>
+    <sheet name="A 2026-2027" sheetId="19" r:id="rId2"/>
+    <sheet name="A 2025-2026" sheetId="18" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="62">
   <si>
     <t>päivä</t>
   </si>
@@ -217,6 +218,12 @@
   </si>
   <si>
     <t>14-25,21-25</t>
+  </si>
+  <si>
+    <t>A-Volley</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
   </si>
 </sst>
 </file>
@@ -764,19 +771,49 @@
         <f>'A 2025-2026'!Q4</f>
         <v>943</v>
       </c>
-      <c r="K2" s="10"/>
+      <c r="K2" s="10">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="27">
+        <f>'A 2026-2027'!R3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="27">
+        <f>'A 2026-2027'!O3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="27">
+        <f>'A 2026-2027'!P3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="27">
+        <f>'A 2026-2027'!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="27">
+        <f>'A 2026-2027'!O4</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="27">
+        <f>'A 2026-2027'!Q4</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="27">
+        <f>'A 2026-2027'!O5</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="27">
+        <f>'A 2026-2027'!Q5</f>
+        <v>0</v>
+      </c>
       <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -785,11 +822,11 @@
         <v>6</v>
       </c>
       <c r="C4" s="11">
-        <f t="shared" ref="C4:J4" si="0">SUM(C2:C3)</f>
+        <f>SUM(C2:C3)</f>
         <v>19</v>
       </c>
       <c r="D4" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D4:J4" si="0">SUM(D2:D3)</f>
         <v>10</v>
       </c>
       <c r="E4" s="11">
@@ -825,7 +862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518CDBF1-FCB5-4B4B-B272-E39FAD5195F0}">
   <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -870,7 +907,7 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>10</v>
@@ -883,7 +920,7 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>45962</v>
       </c>
@@ -891,36 +928,24 @@
         <v>7</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>28</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="20"/>
-      <c r="H2" s="10">
-        <v>1</v>
-      </c>
+      <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
-      <c r="K2" s="10">
-        <v>70</v>
-      </c>
-      <c r="L2" s="10">
-        <v>51</v>
-      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="O2" s="10">
         <f>SUM(H2:H23)+SUM(G2:G23)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P2" s="10">
         <f>SUM(I2:I27)</f>
@@ -928,142 +953,88 @@
       </c>
       <c r="Q2" s="10">
         <f>SUM(J2:J27)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R2" s="10">
         <f>SUM(O2:Q2)</f>
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
-        <v>45962</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="A3" s="23"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="14"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="8">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8">
-        <v>26</v>
-      </c>
-      <c r="L3" s="8">
-        <v>50</v>
-      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H2:H25)*2+SUM(I2:I277)+SUM(G2:G25)*3</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8">
         <f>SUM(J2:J25)*2+SUM(I2:I27)+H9</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(O3:Q3)</f>
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
-        <v>45962</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="10">
-        <v>1</v>
-      </c>
-      <c r="K4" s="10">
-        <v>59</v>
-      </c>
-      <c r="L4" s="10">
-        <v>67</v>
-      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="10">
         <f>SUM(K2:K28)</f>
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
         <f>SUM(L2:L28)</f>
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(O4:Q4)</f>
-        <v>1916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
-        <v>45981</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>37</v>
-      </c>
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
-        <v>28</v>
-      </c>
-      <c r="L5" s="8">
-        <v>50</v>
-      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -1072,36 +1043,18 @@
       <c r="R5" s="8"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
-        <v>45981</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>38</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>38</v>
-      </c>
-      <c r="L6" s="10">
-        <v>50</v>
-      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
@@ -1110,36 +1063,18 @@
       <c r="R6" s="10"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>45981</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8">
-        <v>35</v>
-      </c>
-      <c r="L7" s="8">
-        <v>50</v>
-      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -1147,37 +1082,19 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
     </row>
-    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
-        <v>46004</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="22">
-        <v>1</v>
-      </c>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
-      <c r="K8" s="10">
-        <v>75</v>
-      </c>
-      <c r="L8" s="10">
-        <v>43</v>
-      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
@@ -1185,37 +1102,19 @@
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
     </row>
-    <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>46004</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>44</v>
-      </c>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
+      <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8">
-        <v>69</v>
-      </c>
-      <c r="L9" s="8">
-        <v>67</v>
-      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -1223,37 +1122,19 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
-        <v>46046</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>45</v>
-      </c>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="22"/>
-      <c r="H10" s="10">
-        <v>1</v>
-      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
-      <c r="K10" s="10">
-        <v>66</v>
-      </c>
-      <c r="L10" s="10">
-        <v>49</v>
-      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
@@ -1262,36 +1143,18 @@
       <c r="R10" s="10"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>46046</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>46</v>
-      </c>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8">
-        <v>1</v>
-      </c>
-      <c r="K11" s="8">
-        <v>29</v>
-      </c>
-      <c r="L11" s="8">
-        <v>50</v>
-      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
@@ -1300,36 +1163,18 @@
       <c r="R11" s="8"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
-        <v>46046</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>48</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="10">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10">
-        <v>49</v>
-      </c>
-      <c r="L12" s="10">
-        <v>53</v>
-      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
@@ -1338,36 +1183,18 @@
       <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>46130</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="8">
-        <v>1</v>
-      </c>
+      <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8">
-        <v>52</v>
-      </c>
-      <c r="L13" s="8">
-        <v>48</v>
-      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
@@ -1376,36 +1203,18 @@
       <c r="R13" s="8"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="19">
-        <v>46130</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>52</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="22"/>
-      <c r="H14" s="10">
-        <v>1</v>
-      </c>
+      <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="10">
-        <v>50</v>
-      </c>
-      <c r="L14" s="10">
-        <v>23</v>
-      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
@@ -1414,36 +1223,18 @@
       <c r="R14" s="10"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>46130</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>53</v>
-      </c>
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="8">
-        <v>1</v>
-      </c>
+      <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8">
-        <v>50</v>
-      </c>
-      <c r="L15" s="8">
-        <v>42</v>
-      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
@@ -1451,37 +1242,19 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" spans="1:19" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19">
-        <v>46144</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="10">
-        <v>1</v>
-      </c>
+    <row r="16" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="10">
-        <v>76</v>
-      </c>
-      <c r="L16" s="10">
-        <v>58</v>
-      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
@@ -1490,36 +1263,18 @@
       <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:18" s="28" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
-        <v>46144</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="26">
-        <v>1</v>
-      </c>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="27"/>
       <c r="I17" s="27"/>
       <c r="J17" s="27"/>
-      <c r="K17" s="27">
-        <v>75</v>
-      </c>
-      <c r="L17" s="27">
-        <v>45</v>
-      </c>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
       <c r="M17" s="27"/>
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
@@ -1528,36 +1283,18 @@
       <c r="R17" s="27"/>
     </row>
     <row r="18" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
-        <v>46157</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>57</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="10">
-        <v>1</v>
-      </c>
+      <c r="H18" s="10"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
-      <c r="K18" s="10">
-        <v>58</v>
-      </c>
-      <c r="L18" s="10">
-        <v>47</v>
-      </c>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
@@ -1566,36 +1303,18 @@
       <c r="R18" s="10"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="18">
-        <v>46157</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>58</v>
-      </c>
+      <c r="A19" s="18"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8">
-        <v>33</v>
-      </c>
-      <c r="L19" s="8">
-        <v>50</v>
-      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
@@ -1604,36 +1323,18 @@
       <c r="R19" s="8"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="19">
-        <v>46157</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>59</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="10">
-        <v>1</v>
-      </c>
-      <c r="K20" s="10">
-        <v>35</v>
-      </c>
-      <c r="L20" s="10">
-        <v>50</v>
-      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
@@ -1737,4 +1438,919 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="18" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="9">
+        <v>3</v>
+      </c>
+      <c r="H1" s="9">
+        <v>2</v>
+      </c>
+      <c r="I1" s="9">
+        <v>1</v>
+      </c>
+      <c r="J1" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="19">
+        <v>45962</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="10">
+        <v>1</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10">
+        <v>70</v>
+      </c>
+      <c r="L2" s="10">
+        <v>51</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="10">
+        <f>SUM(H2:H23)+SUM(G2:G23)</f>
+        <v>10</v>
+      </c>
+      <c r="P2" s="10">
+        <f>SUM(I2:I27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="10">
+        <f>SUM(J2:J27)</f>
+        <v>9</v>
+      </c>
+      <c r="R2" s="10">
+        <f>SUM(O2:Q2)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
+        <v>45962</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8">
+        <v>26</v>
+      </c>
+      <c r="L3" s="8">
+        <v>50</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="8">
+        <f>SUM(H2:H25)*2+SUM(I2:I277)+SUM(G2:G25)*3</f>
+        <v>23</v>
+      </c>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8">
+        <f>SUM(J2:J25)*2+SUM(I2:I27)+H9</f>
+        <v>19</v>
+      </c>
+      <c r="R3" s="8">
+        <f>SUM(O3:Q3)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>45962</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10">
+        <v>59</v>
+      </c>
+      <c r="L4" s="10">
+        <v>67</v>
+      </c>
+      <c r="M4" s="10"/>
+      <c r="N4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="10">
+        <f>SUM(K2:K28)</f>
+        <v>973</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10">
+        <f>SUM(L2:L28)</f>
+        <v>943</v>
+      </c>
+      <c r="R4" s="10">
+        <f>SUM(O4:Q4)</f>
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>45981</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>28</v>
+      </c>
+      <c r="L5" s="8">
+        <v>50</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>45981</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
+        <v>38</v>
+      </c>
+      <c r="L6" s="10">
+        <v>50</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>45981</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>35</v>
+      </c>
+      <c r="L7" s="8">
+        <v>50</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>46004</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="22">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10">
+        <v>75</v>
+      </c>
+      <c r="L8" s="10">
+        <v>43</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46004</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8">
+        <v>69</v>
+      </c>
+      <c r="L9" s="8">
+        <v>67</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>46046</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <v>66</v>
+      </c>
+      <c r="L10" s="10">
+        <v>49</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46046</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>29</v>
+      </c>
+      <c r="L11" s="8">
+        <v>50</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>46046</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>49</v>
+      </c>
+      <c r="L12" s="10">
+        <v>53</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46130</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8">
+        <v>52</v>
+      </c>
+      <c r="L13" s="8">
+        <v>48</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>46130</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="10">
+        <v>1</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10">
+        <v>50</v>
+      </c>
+      <c r="L14" s="10">
+        <v>23</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46130</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
+        <v>50</v>
+      </c>
+      <c r="L15" s="8">
+        <v>42</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:19" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>46144</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10">
+        <v>76</v>
+      </c>
+      <c r="L16" s="10">
+        <v>58</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+    </row>
+    <row r="17" spans="1:18" s="28" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23">
+        <v>46144</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="26">
+        <v>1</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27">
+        <v>75</v>
+      </c>
+      <c r="L17" s="27">
+        <v>45</v>
+      </c>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+    </row>
+    <row r="18" spans="1:18" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>46157</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10">
+        <v>58</v>
+      </c>
+      <c r="L18" s="10">
+        <v>47</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>46157</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <v>33</v>
+      </c>
+      <c r="L19" s="8">
+        <v>50</v>
+      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="19">
+        <v>46157</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="22"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10">
+        <v>35</v>
+      </c>
+      <c r="L20" s="10">
+        <v>50</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>